--- a/260414 - BREEAM V7 - VEELAGE SBY 9.4.1.xlsx
+++ b/260414 - BREEAM V7 - VEELAGE SBY 9.4.1.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1AD1FB0-1A54-480B-8AF9-77F53729E12B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7660EDCE-C832-43A9-B389-B997603951EF}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Evaluation" sheetId="3" r:id="rId1"/>
@@ -19,7 +18,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">Evaluation!$A$1:$N$142</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Points à prendre'!$F$3:$N$10</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -2999,7 +2998,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.000%"/>
@@ -3937,13 +3936,22 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="11" fillId="11" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="11" fillId="11" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="11" fillId="11" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="11" fillId="11" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="11" fillId="11" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="11" fillId="11" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="11" fillId="5" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="11" fillId="5" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="11" fillId="5" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="11" fillId="5" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3953,24 +3961,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="11" fillId="5" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="11" fillId="11" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="11" fillId="11" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="11" fillId="11" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="11" fillId="5" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="11" fillId="5" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="11" fillId="5" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4009,50 +3999,32 @@
     <xf numFmtId="10" fontId="12" fillId="10" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="11" fillId="11" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="11" fillId="11" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="11" fillId="11" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="11" fillId="11" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="11" fillId="11" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="11" fillId="11" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="12" fillId="7" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="12" fillId="7" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="12" fillId="7" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="12" fillId="7" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4072,25 +4044,52 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="10" fontId="12" fillId="7" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="11" fillId="5" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="12" fillId="7" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="11" fillId="5" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="12" fillId="7" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="11" fillId="5" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="11" fillId="5" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="11" fillId="11" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="11" fillId="5" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="11" fillId="11" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="11" fillId="5" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="11" fillId="11" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="12" fillId="7" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="12" fillId="7" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4100,20 +4099,6 @@
     <cellStyle name="Pourcentage" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="15">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -4417,6 +4402,20 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -10977,27 +10976,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tableau5" displayName="Tableau5" ref="F3:N18" totalsRowCount="1" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11">
-  <autoFilter ref="F3:N17" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Tableau5" displayName="Tableau5" ref="F3:N18" totalsRowCount="1" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11" tableBorderDxfId="9">
+  <autoFilter ref="F3:N17"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Crédit" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Action" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Critère" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Estimation du nombre de points atteignables" totalsRowFunction="sum" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Nombre de points atteignables" totalsRowFunction="sum" dataDxfId="6" dataCellStyle="Pourcentage"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Coût H.T. (estimation)" dataDxfId="5" dataCellStyle="Monétaire"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Commentaire" dataDxfId="4"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Responsable" dataDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="mission sous traitée" dataDxfId="2"/>
+    <tableColumn id="1" name="Crédit" dataDxfId="8"/>
+    <tableColumn id="2" name="Action" dataDxfId="7"/>
+    <tableColumn id="3" name="Critère" dataDxfId="6"/>
+    <tableColumn id="7" name="Estimation du nombre de points atteignables" totalsRowFunction="sum" dataDxfId="5"/>
+    <tableColumn id="8" name="Nombre de points atteignables" totalsRowFunction="sum" dataDxfId="4" dataCellStyle="Pourcentage"/>
+    <tableColumn id="9" name="Coût H.T. (estimation)" dataDxfId="3" dataCellStyle="Monétaire"/>
+    <tableColumn id="10" name="Commentaire" dataDxfId="2"/>
+    <tableColumn id="13" name="Responsable" dataDxfId="1"/>
+    <tableColumn id="11" name="mission sous traitée" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -11035,9 +11034,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -11072,7 +11071,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -11107,7 +11106,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -11280,7 +11279,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -11382,7 +11381,7 @@
       <c r="M2" s="50"/>
       <c r="N2" s="48"/>
     </row>
-    <row r="3" spans="1:14" ht="90" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>13</v>
       </c>
@@ -12483,7 +12482,7 @@
       <c r="M30" s="51"/>
       <c r="N30" s="48"/>
     </row>
-    <row r="31" spans="1:14" ht="90" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="23" t="s">
         <v>249</v>
       </c>
@@ -13105,7 +13104,7 @@
       <c r="M46" s="51"/>
       <c r="N46" s="48"/>
     </row>
-    <row r="47" spans="1:14" ht="195" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="23" t="s">
         <v>23</v>
       </c>
@@ -13259,7 +13258,7 @@
       <c r="M50" s="52"/>
       <c r="N50" s="48"/>
     </row>
-    <row r="51" spans="1:14" ht="330" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" ht="330" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="23" t="s">
         <v>24</v>
       </c>
@@ -16054,7 +16053,7 @@
       <c r="M123" s="51"/>
       <c r="N123" s="48"/>
     </row>
-    <row r="124" spans="1:14" ht="180" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:14" ht="228.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="23" t="s">
         <v>540</v>
       </c>
@@ -16755,7 +16754,7 @@
       <c r="N142" s="52"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N142" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <autoFilter ref="A1:N142">
     <filterColumn colId="0" showButton="0"/>
     <filterColumn colId="5">
       <filters>
@@ -16782,7 +16781,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AB69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -16861,7 +16860,7 @@
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A2" s="138" t="s">
+      <c r="A2" s="141" t="s">
         <v>204</v>
       </c>
       <c r="B2" s="71" t="s">
@@ -16883,35 +16882,35 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B2&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>3</v>
       </c>
-      <c r="G2" s="153">
+      <c r="G2" s="144">
         <f>SUM(C2:C6)</f>
         <v>15</v>
       </c>
-      <c r="H2" s="156">
+      <c r="H2" s="147">
         <f>SUM(D2:D6)</f>
         <v>8</v>
       </c>
-      <c r="I2" s="147">
+      <c r="I2" s="150">
         <f t="shared" ref="I2" si="0">SUM(E2:E6)</f>
         <v>11</v>
       </c>
-      <c r="J2" s="147">
+      <c r="J2" s="150">
         <f t="shared" ref="J2" si="1">SUM(F2:F6)</f>
         <v>18</v>
       </c>
-      <c r="K2" s="159">
+      <c r="K2" s="153">
         <f>Q3/G2</f>
         <v>7.3333333333333332E-3</v>
       </c>
-      <c r="L2" s="123">
+      <c r="L2" s="156">
         <f>H2*K2</f>
         <v>5.8666666666666666E-2</v>
       </c>
-      <c r="M2" s="117">
+      <c r="M2" s="120">
         <f>I2*K2</f>
         <v>8.0666666666666664E-2</v>
       </c>
-      <c r="N2" s="160">
+      <c r="N2" s="117">
         <f>J2*K2</f>
         <v>0.13200000000000001</v>
       </c>
@@ -16953,7 +16952,7 @@
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A3" s="139"/>
+      <c r="A3" s="142"/>
       <c r="B3" s="76" t="s">
         <v>14</v>
       </c>
@@ -16973,14 +16972,14 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B3&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>3</v>
       </c>
-      <c r="G3" s="154"/>
-      <c r="H3" s="157"/>
-      <c r="I3" s="148"/>
-      <c r="J3" s="148"/>
-      <c r="K3" s="151"/>
-      <c r="L3" s="124"/>
-      <c r="M3" s="118"/>
-      <c r="N3" s="161"/>
+      <c r="G3" s="145"/>
+      <c r="H3" s="148"/>
+      <c r="I3" s="151"/>
+      <c r="J3" s="151"/>
+      <c r="K3" s="154"/>
+      <c r="L3" s="157"/>
+      <c r="M3" s="121"/>
+      <c r="N3" s="118"/>
       <c r="P3" s="66" t="str">
         <f>$A$2</f>
         <v>Management</v>
@@ -17028,7 +17027,7 @@
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A4" s="139"/>
+      <c r="A4" s="142"/>
       <c r="B4" s="76" t="s">
         <v>15</v>
       </c>
@@ -17048,14 +17047,14 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B4&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>6</v>
       </c>
-      <c r="G4" s="154"/>
-      <c r="H4" s="157"/>
-      <c r="I4" s="148"/>
-      <c r="J4" s="148"/>
-      <c r="K4" s="151"/>
-      <c r="L4" s="124"/>
-      <c r="M4" s="118"/>
-      <c r="N4" s="161"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="151"/>
+      <c r="J4" s="151"/>
+      <c r="K4" s="154"/>
+      <c r="L4" s="157"/>
+      <c r="M4" s="121"/>
+      <c r="N4" s="118"/>
       <c r="P4" s="66" t="str">
         <f>$A$7</f>
         <v>Health and Wellbeing</v>
@@ -17103,7 +17102,7 @@
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A5" s="139"/>
+      <c r="A5" s="142"/>
       <c r="B5" s="76" t="s">
         <v>16</v>
       </c>
@@ -17123,14 +17122,14 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B5&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>4</v>
       </c>
-      <c r="G5" s="154"/>
-      <c r="H5" s="157"/>
-      <c r="I5" s="148"/>
-      <c r="J5" s="148"/>
-      <c r="K5" s="151"/>
-      <c r="L5" s="124"/>
-      <c r="M5" s="118"/>
-      <c r="N5" s="161"/>
+      <c r="G5" s="145"/>
+      <c r="H5" s="148"/>
+      <c r="I5" s="151"/>
+      <c r="J5" s="151"/>
+      <c r="K5" s="154"/>
+      <c r="L5" s="157"/>
+      <c r="M5" s="121"/>
+      <c r="N5" s="118"/>
       <c r="P5" s="66" t="str">
         <f>$A$17</f>
         <v>Energy</v>
@@ -17178,7 +17177,7 @@
       </c>
     </row>
     <row r="6" spans="1:28" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="145"/>
+      <c r="A6" s="143"/>
       <c r="B6" s="81" t="s">
         <v>17</v>
       </c>
@@ -17198,14 +17197,14 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B6&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>2</v>
       </c>
-      <c r="G6" s="155"/>
-      <c r="H6" s="158"/>
-      <c r="I6" s="149"/>
-      <c r="J6" s="149"/>
-      <c r="K6" s="152"/>
-      <c r="L6" s="125"/>
-      <c r="M6" s="119"/>
-      <c r="N6" s="162"/>
+      <c r="G6" s="146"/>
+      <c r="H6" s="149"/>
+      <c r="I6" s="152"/>
+      <c r="J6" s="152"/>
+      <c r="K6" s="155"/>
+      <c r="L6" s="158"/>
+      <c r="M6" s="122"/>
+      <c r="N6" s="119"/>
       <c r="P6" s="66" t="str">
         <f>$A$25</f>
         <v>Transport</v>
@@ -17253,7 +17252,7 @@
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A7" s="126" t="s">
+      <c r="A7" s="123" t="s">
         <v>205</v>
       </c>
       <c r="B7" s="83" t="s">
@@ -17275,35 +17274,35 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B7&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>1</v>
       </c>
-      <c r="G7" s="129">
+      <c r="G7" s="126">
         <f>SUM(C7:C16)-C15</f>
         <v>6</v>
       </c>
-      <c r="H7" s="132">
+      <c r="H7" s="129">
         <f>SUM(D7:D16)-D15</f>
         <v>2</v>
       </c>
-      <c r="I7" s="132">
+      <c r="I7" s="129">
         <f t="shared" ref="I7:J7" si="7">SUM(E7:E16)-E15</f>
         <v>3</v>
       </c>
-      <c r="J7" s="132">
+      <c r="J7" s="129">
         <f t="shared" si="7"/>
         <v>16</v>
       </c>
-      <c r="K7" s="135">
+      <c r="K7" s="132">
         <f>Q4/G7</f>
         <v>3.1666666666666669E-2</v>
       </c>
-      <c r="L7" s="120">
+      <c r="L7" s="135">
         <f>H7*$K$7+D15*$Q$13</f>
         <v>7.8333333333333338E-2</v>
       </c>
-      <c r="M7" s="114">
+      <c r="M7" s="138">
         <f>I7*$K$7+E15*$Q$13</f>
         <v>0.11</v>
       </c>
-      <c r="N7" s="163">
+      <c r="N7" s="114">
         <f>J7*$K$7+F15*$Q$13</f>
         <v>0.52166666666666672</v>
       </c>
@@ -17354,7 +17353,7 @@
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A8" s="127"/>
+      <c r="A8" s="124"/>
       <c r="B8" s="85" t="s">
         <v>19</v>
       </c>
@@ -17374,14 +17373,14 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B8&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>2</v>
       </c>
-      <c r="G8" s="130"/>
-      <c r="H8" s="133"/>
-      <c r="I8" s="133"/>
-      <c r="J8" s="133"/>
-      <c r="K8" s="136"/>
-      <c r="L8" s="121"/>
-      <c r="M8" s="115"/>
-      <c r="N8" s="164"/>
+      <c r="G8" s="127"/>
+      <c r="H8" s="130"/>
+      <c r="I8" s="130"/>
+      <c r="J8" s="130"/>
+      <c r="K8" s="133"/>
+      <c r="L8" s="136"/>
+      <c r="M8" s="139"/>
+      <c r="N8" s="115"/>
       <c r="P8" s="66" t="str">
         <f>$A$32</f>
         <v>Materials</v>
@@ -17429,7 +17428,7 @@
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A9" s="127"/>
+      <c r="A9" s="124"/>
       <c r="B9" s="85" t="s">
         <v>20</v>
       </c>
@@ -17449,14 +17448,14 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B9&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>0</v>
       </c>
-      <c r="G9" s="130"/>
-      <c r="H9" s="133"/>
-      <c r="I9" s="133"/>
-      <c r="J9" s="133"/>
-      <c r="K9" s="136"/>
-      <c r="L9" s="121"/>
-      <c r="M9" s="115"/>
-      <c r="N9" s="164"/>
+      <c r="G9" s="127"/>
+      <c r="H9" s="130"/>
+      <c r="I9" s="130"/>
+      <c r="J9" s="130"/>
+      <c r="K9" s="133"/>
+      <c r="L9" s="136"/>
+      <c r="M9" s="139"/>
+      <c r="N9" s="115"/>
       <c r="P9" s="66" t="str">
         <f>$A$37</f>
         <v>Waste</v>
@@ -17504,7 +17503,7 @@
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A10" s="127"/>
+      <c r="A10" s="124"/>
       <c r="B10" s="85" t="s">
         <v>21</v>
       </c>
@@ -17524,14 +17523,14 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B10&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>4</v>
       </c>
-      <c r="G10" s="130"/>
-      <c r="H10" s="133"/>
-      <c r="I10" s="133"/>
-      <c r="J10" s="133"/>
-      <c r="K10" s="136"/>
-      <c r="L10" s="121"/>
-      <c r="M10" s="115"/>
-      <c r="N10" s="164"/>
+      <c r="G10" s="127"/>
+      <c r="H10" s="130"/>
+      <c r="I10" s="130"/>
+      <c r="J10" s="130"/>
+      <c r="K10" s="133"/>
+      <c r="L10" s="136"/>
+      <c r="M10" s="139"/>
+      <c r="N10" s="115"/>
       <c r="P10" s="66" t="str">
         <f>$A$43</f>
         <v>Land Use and ecology</v>
@@ -17579,7 +17578,7 @@
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A11" s="127"/>
+      <c r="A11" s="124"/>
       <c r="B11" s="85" t="s">
         <v>22</v>
       </c>
@@ -17599,14 +17598,14 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B11&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>3</v>
       </c>
-      <c r="G11" s="130"/>
-      <c r="H11" s="133"/>
-      <c r="I11" s="133"/>
-      <c r="J11" s="133"/>
-      <c r="K11" s="136"/>
-      <c r="L11" s="121"/>
-      <c r="M11" s="115"/>
-      <c r="N11" s="164"/>
+      <c r="G11" s="127"/>
+      <c r="H11" s="130"/>
+      <c r="I11" s="130"/>
+      <c r="J11" s="130"/>
+      <c r="K11" s="133"/>
+      <c r="L11" s="136"/>
+      <c r="M11" s="139"/>
+      <c r="N11" s="115"/>
       <c r="P11" s="66" t="str">
         <f>$A$48</f>
         <v>Pollution</v>
@@ -17654,7 +17653,7 @@
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A12" s="127"/>
+      <c r="A12" s="124"/>
       <c r="B12" s="85" t="s">
         <v>23</v>
       </c>
@@ -17674,14 +17673,14 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B12&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>3</v>
       </c>
-      <c r="G12" s="130"/>
-      <c r="H12" s="133"/>
-      <c r="I12" s="133"/>
-      <c r="J12" s="133"/>
-      <c r="K12" s="136"/>
-      <c r="L12" s="121"/>
-      <c r="M12" s="115"/>
-      <c r="N12" s="164"/>
+      <c r="G12" s="127"/>
+      <c r="H12" s="130"/>
+      <c r="I12" s="130"/>
+      <c r="J12" s="130"/>
+      <c r="K12" s="133"/>
+      <c r="L12" s="136"/>
+      <c r="M12" s="139"/>
+      <c r="N12" s="115"/>
       <c r="P12" s="66" t="str">
         <f>$A$53</f>
         <v>Innovation</v>
@@ -17729,7 +17728,7 @@
       </c>
     </row>
     <row r="13" spans="1:28" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="127"/>
+      <c r="A13" s="124"/>
       <c r="B13" s="89" t="s">
         <v>24</v>
       </c>
@@ -17749,14 +17748,14 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B13&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>2</v>
       </c>
-      <c r="G13" s="130"/>
-      <c r="H13" s="133"/>
-      <c r="I13" s="133"/>
-      <c r="J13" s="133"/>
-      <c r="K13" s="136"/>
-      <c r="L13" s="121"/>
-      <c r="M13" s="115"/>
-      <c r="N13" s="164"/>
+      <c r="G13" s="127"/>
+      <c r="H13" s="130"/>
+      <c r="I13" s="130"/>
+      <c r="J13" s="130"/>
+      <c r="K13" s="133"/>
+      <c r="L13" s="136"/>
+      <c r="M13" s="139"/>
+      <c r="N13" s="115"/>
       <c r="P13" s="91" t="s">
         <v>243</v>
       </c>
@@ -17782,7 +17781,7 @@
       </c>
     </row>
     <row r="14" spans="1:28" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="127"/>
+      <c r="A14" s="124"/>
       <c r="B14" s="89" t="s">
         <v>157</v>
       </c>
@@ -17802,14 +17801,14 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B14&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>0</v>
       </c>
-      <c r="G14" s="130"/>
-      <c r="H14" s="133"/>
-      <c r="I14" s="133"/>
-      <c r="J14" s="133"/>
-      <c r="K14" s="136"/>
-      <c r="L14" s="121"/>
-      <c r="M14" s="115"/>
-      <c r="N14" s="164"/>
+      <c r="G14" s="127"/>
+      <c r="H14" s="130"/>
+      <c r="I14" s="130"/>
+      <c r="J14" s="130"/>
+      <c r="K14" s="133"/>
+      <c r="L14" s="136"/>
+      <c r="M14" s="139"/>
+      <c r="N14" s="115"/>
       <c r="P14" s="92" t="s">
         <v>207</v>
       </c>
@@ -17828,7 +17827,7 @@
       </c>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A15" s="127"/>
+      <c r="A15" s="124"/>
       <c r="B15" s="89" t="s">
         <v>264</v>
       </c>
@@ -17848,14 +17847,14 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B15&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>1</v>
       </c>
-      <c r="G15" s="130"/>
-      <c r="H15" s="133"/>
-      <c r="I15" s="133"/>
-      <c r="J15" s="133"/>
-      <c r="K15" s="136"/>
-      <c r="L15" s="121"/>
-      <c r="M15" s="115"/>
-      <c r="N15" s="164"/>
+      <c r="G15" s="127"/>
+      <c r="H15" s="130"/>
+      <c r="I15" s="130"/>
+      <c r="J15" s="130"/>
+      <c r="K15" s="133"/>
+      <c r="L15" s="136"/>
+      <c r="M15" s="139"/>
+      <c r="N15" s="115"/>
       <c r="P15" s="96"/>
       <c r="R15" s="97" t="str">
         <f>IF(R14&lt;0.3,"UNCLASSIFIED",IF(R14&lt;0.45,"PASS",IF(R14&lt;0.55,"GOOD",IF(R14&lt;0.7,"VERY GOOD",IF(R14&lt;0.85,"EXCELLENT","OUTSTANDING")))))</f>
@@ -17871,7 +17870,7 @@
       </c>
     </row>
     <row r="16" spans="1:28" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="128"/>
+      <c r="A16" s="125"/>
       <c r="B16" s="98" t="s">
         <v>266</v>
       </c>
@@ -17891,19 +17890,19 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B16&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>1</v>
       </c>
-      <c r="G16" s="131"/>
-      <c r="H16" s="134"/>
-      <c r="I16" s="134"/>
-      <c r="J16" s="134"/>
-      <c r="K16" s="137"/>
-      <c r="L16" s="122"/>
-      <c r="M16" s="116"/>
-      <c r="N16" s="165"/>
+      <c r="G16" s="128"/>
+      <c r="H16" s="131"/>
+      <c r="I16" s="131"/>
+      <c r="J16" s="131"/>
+      <c r="K16" s="134"/>
+      <c r="L16" s="137"/>
+      <c r="M16" s="140"/>
+      <c r="N16" s="116"/>
       <c r="P16" s="96"/>
       <c r="Q16" s="100"/>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A17" s="138" t="s">
+      <c r="A17" s="141" t="s">
         <v>206</v>
       </c>
       <c r="B17" s="71" t="s">
@@ -17925,35 +17924,35 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B17&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>8</v>
       </c>
-      <c r="G17" s="140">
+      <c r="G17" s="159">
         <f>SUM(C17:C24)</f>
         <v>14</v>
       </c>
-      <c r="H17" s="147">
+      <c r="H17" s="150">
         <f>SUM(D17:D24)</f>
         <v>6</v>
       </c>
-      <c r="I17" s="147">
+      <c r="I17" s="150">
         <f>SUM(E17:E24)</f>
         <v>11</v>
       </c>
-      <c r="J17" s="147">
+      <c r="J17" s="150">
         <f>SUM(F17:F24)</f>
         <v>32</v>
       </c>
-      <c r="K17" s="150">
+      <c r="K17" s="161">
         <f>Q5/G17</f>
         <v>1.1428571428571429E-2</v>
       </c>
-      <c r="L17" s="123">
+      <c r="L17" s="156">
         <f>H17*K17</f>
         <v>6.8571428571428575E-2</v>
       </c>
-      <c r="M17" s="117">
+      <c r="M17" s="120">
         <f>I17*K17</f>
         <v>0.12571428571428572</v>
       </c>
-      <c r="N17" s="160">
+      <c r="N17" s="117">
         <f>J17*K17</f>
         <v>0.36571428571428571</v>
       </c>
@@ -17974,7 +17973,7 @@
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A18" s="139"/>
+      <c r="A18" s="142"/>
       <c r="B18" s="76" t="s">
         <v>26</v>
       </c>
@@ -17994,14 +17993,14 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B18&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>10</v>
       </c>
-      <c r="G18" s="141"/>
-      <c r="H18" s="148"/>
-      <c r="I18" s="148"/>
-      <c r="J18" s="148"/>
-      <c r="K18" s="151"/>
-      <c r="L18" s="124"/>
-      <c r="M18" s="118"/>
-      <c r="N18" s="161"/>
+      <c r="G18" s="160"/>
+      <c r="H18" s="151"/>
+      <c r="I18" s="151"/>
+      <c r="J18" s="151"/>
+      <c r="K18" s="154"/>
+      <c r="L18" s="157"/>
+      <c r="M18" s="121"/>
+      <c r="N18" s="118"/>
       <c r="Q18" s="66" t="s">
         <v>210</v>
       </c>
@@ -18019,7 +18018,7 @@
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A19" s="139"/>
+      <c r="A19" s="142"/>
       <c r="B19" s="76" t="s">
         <v>27</v>
       </c>
@@ -18039,14 +18038,14 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B19&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>2</v>
       </c>
-      <c r="G19" s="141"/>
-      <c r="H19" s="148"/>
-      <c r="I19" s="148"/>
-      <c r="J19" s="148"/>
-      <c r="K19" s="151"/>
-      <c r="L19" s="124"/>
-      <c r="M19" s="118"/>
-      <c r="N19" s="161"/>
+      <c r="G19" s="160"/>
+      <c r="H19" s="151"/>
+      <c r="I19" s="151"/>
+      <c r="J19" s="151"/>
+      <c r="K19" s="154"/>
+      <c r="L19" s="157"/>
+      <c r="M19" s="121"/>
+      <c r="N19" s="118"/>
       <c r="Q19" s="66" t="s">
         <v>212</v>
       </c>
@@ -18064,7 +18063,7 @@
       </c>
     </row>
     <row r="20" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="139"/>
+      <c r="A20" s="142"/>
       <c r="B20" s="76" t="s">
         <v>28</v>
       </c>
@@ -18084,14 +18083,14 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B20&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>3</v>
       </c>
-      <c r="G20" s="141"/>
-      <c r="H20" s="148"/>
-      <c r="I20" s="148"/>
-      <c r="J20" s="148"/>
-      <c r="K20" s="151"/>
-      <c r="L20" s="124"/>
-      <c r="M20" s="118"/>
-      <c r="N20" s="161"/>
+      <c r="G20" s="160"/>
+      <c r="H20" s="151"/>
+      <c r="I20" s="151"/>
+      <c r="J20" s="151"/>
+      <c r="K20" s="154"/>
+      <c r="L20" s="157"/>
+      <c r="M20" s="121"/>
+      <c r="N20" s="118"/>
       <c r="Q20" s="66" t="s">
         <v>213</v>
       </c>
@@ -18109,7 +18108,7 @@
       </c>
     </row>
     <row r="21" spans="1:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="139"/>
+      <c r="A21" s="142"/>
       <c r="B21" s="76" t="s">
         <v>29</v>
       </c>
@@ -18129,14 +18128,14 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B21&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>3</v>
       </c>
-      <c r="G21" s="141"/>
-      <c r="H21" s="148"/>
-      <c r="I21" s="148"/>
-      <c r="J21" s="148"/>
-      <c r="K21" s="151"/>
-      <c r="L21" s="124"/>
-      <c r="M21" s="118"/>
-      <c r="N21" s="161"/>
+      <c r="G21" s="160"/>
+      <c r="H21" s="151"/>
+      <c r="I21" s="151"/>
+      <c r="J21" s="151"/>
+      <c r="K21" s="154"/>
+      <c r="L21" s="157"/>
+      <c r="M21" s="121"/>
+      <c r="N21" s="118"/>
       <c r="Q21" s="66" t="s">
         <v>214</v>
       </c>
@@ -18154,7 +18153,7 @@
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A22" s="139"/>
+      <c r="A22" s="142"/>
       <c r="B22" s="76" t="s">
         <v>30</v>
       </c>
@@ -18174,14 +18173,14 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B22&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>5</v>
       </c>
-      <c r="G22" s="141"/>
-      <c r="H22" s="148"/>
-      <c r="I22" s="148"/>
-      <c r="J22" s="148"/>
-      <c r="K22" s="151"/>
-      <c r="L22" s="124"/>
-      <c r="M22" s="118"/>
-      <c r="N22" s="161"/>
+      <c r="G22" s="160"/>
+      <c r="H22" s="151"/>
+      <c r="I22" s="151"/>
+      <c r="J22" s="151"/>
+      <c r="K22" s="154"/>
+      <c r="L22" s="157"/>
+      <c r="M22" s="121"/>
+      <c r="N22" s="118"/>
       <c r="Q22" s="66" t="s">
         <v>215</v>
       </c>
@@ -18199,7 +18198,7 @@
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A23" s="139"/>
+      <c r="A23" s="142"/>
       <c r="B23" s="76" t="s">
         <v>31</v>
       </c>
@@ -18219,17 +18218,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B23&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>0</v>
       </c>
-      <c r="G23" s="141"/>
-      <c r="H23" s="148"/>
-      <c r="I23" s="148"/>
-      <c r="J23" s="148"/>
-      <c r="K23" s="151"/>
-      <c r="L23" s="124"/>
-      <c r="M23" s="118"/>
-      <c r="N23" s="161"/>
+      <c r="G23" s="160"/>
+      <c r="H23" s="151"/>
+      <c r="I23" s="151"/>
+      <c r="J23" s="151"/>
+      <c r="K23" s="154"/>
+      <c r="L23" s="157"/>
+      <c r="M23" s="121"/>
+      <c r="N23" s="118"/>
     </row>
     <row r="24" spans="1:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="139"/>
+      <c r="A24" s="142"/>
       <c r="B24" s="76" t="s">
         <v>32</v>
       </c>
@@ -18249,17 +18248,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B24&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>1</v>
       </c>
-      <c r="G24" s="141"/>
-      <c r="H24" s="148"/>
-      <c r="I24" s="148"/>
-      <c r="J24" s="148"/>
-      <c r="K24" s="152"/>
-      <c r="L24" s="125"/>
-      <c r="M24" s="119"/>
-      <c r="N24" s="162"/>
+      <c r="G24" s="160"/>
+      <c r="H24" s="151"/>
+      <c r="I24" s="151"/>
+      <c r="J24" s="151"/>
+      <c r="K24" s="155"/>
+      <c r="L24" s="158"/>
+      <c r="M24" s="122"/>
+      <c r="N24" s="119"/>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A25" s="126" t="s">
+      <c r="A25" s="123" t="s">
         <v>209</v>
       </c>
       <c r="B25" s="83" t="s">
@@ -18281,41 +18280,41 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B25&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>2</v>
       </c>
-      <c r="G25" s="129">
+      <c r="G25" s="126">
         <f>SUM(C25:C26)</f>
         <v>12</v>
       </c>
-      <c r="H25" s="132">
+      <c r="H25" s="129">
         <f>SUM(D25:D26)</f>
         <v>5</v>
       </c>
-      <c r="I25" s="132">
+      <c r="I25" s="129">
         <f>SUM(E25:E26)</f>
         <v>6</v>
       </c>
-      <c r="J25" s="132">
+      <c r="J25" s="129">
         <f>SUM(F25:F26)</f>
         <v>10</v>
       </c>
-      <c r="K25" s="135">
+      <c r="K25" s="132">
         <f>Q6/G25</f>
         <v>6.6666666666666671E-3</v>
       </c>
-      <c r="L25" s="120">
+      <c r="L25" s="135">
         <f>H25*K25</f>
         <v>3.3333333333333333E-2</v>
       </c>
-      <c r="M25" s="114">
+      <c r="M25" s="138">
         <f>I25*K25</f>
         <v>0.04</v>
       </c>
-      <c r="N25" s="163">
+      <c r="N25" s="114">
         <f>J25*K25</f>
         <v>6.6666666666666666E-2</v>
       </c>
     </row>
     <row r="26" spans="1:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="127"/>
+      <c r="A26" s="124"/>
       <c r="B26" s="85" t="s">
         <v>11</v>
       </c>
@@ -18335,17 +18334,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B26&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>8</v>
       </c>
-      <c r="G26" s="130"/>
-      <c r="H26" s="133"/>
-      <c r="I26" s="133"/>
-      <c r="J26" s="133"/>
-      <c r="K26" s="137"/>
-      <c r="L26" s="122"/>
-      <c r="M26" s="116"/>
-      <c r="N26" s="165"/>
+      <c r="G26" s="127"/>
+      <c r="H26" s="130"/>
+      <c r="I26" s="130"/>
+      <c r="J26" s="130"/>
+      <c r="K26" s="134"/>
+      <c r="L26" s="137"/>
+      <c r="M26" s="140"/>
+      <c r="N26" s="116"/>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A27" s="138" t="s">
+      <c r="A27" s="141" t="s">
         <v>211</v>
       </c>
       <c r="B27" s="71" t="s">
@@ -18367,41 +18366,41 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B27&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>4</v>
       </c>
-      <c r="G27" s="140">
+      <c r="G27" s="159">
         <f>SUM(C27:C31)</f>
         <v>2</v>
       </c>
-      <c r="H27" s="147">
+      <c r="H27" s="150">
         <f>SUM(D27:D31)</f>
         <v>1</v>
       </c>
-      <c r="I27" s="147">
+      <c r="I27" s="150">
         <f t="shared" ref="I27:J27" si="10">SUM(E27:E31)</f>
         <v>1</v>
       </c>
-      <c r="J27" s="147">
+      <c r="J27" s="150">
         <f t="shared" si="10"/>
         <v>8</v>
       </c>
-      <c r="K27" s="150">
+      <c r="K27" s="161">
         <f>IF(G27=0,0,Q7/G27)</f>
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="L27" s="123">
+      <c r="L27" s="156">
         <f>H27*K27</f>
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="M27" s="117">
+      <c r="M27" s="120">
         <f>I27*K27</f>
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="N27" s="160">
+      <c r="N27" s="117">
         <f>J27*K27</f>
         <v>0.3</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A28" s="139"/>
+      <c r="A28" s="142"/>
       <c r="B28" s="76" t="s">
         <v>9</v>
       </c>
@@ -18421,17 +18420,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B28&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>1</v>
       </c>
-      <c r="G28" s="141"/>
-      <c r="H28" s="148"/>
-      <c r="I28" s="148"/>
-      <c r="J28" s="148"/>
-      <c r="K28" s="151"/>
-      <c r="L28" s="124"/>
-      <c r="M28" s="118"/>
-      <c r="N28" s="161"/>
+      <c r="G28" s="160"/>
+      <c r="H28" s="151"/>
+      <c r="I28" s="151"/>
+      <c r="J28" s="151"/>
+      <c r="K28" s="154"/>
+      <c r="L28" s="157"/>
+      <c r="M28" s="121"/>
+      <c r="N28" s="118"/>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A29" s="139"/>
+      <c r="A29" s="142"/>
       <c r="B29" s="76" t="s">
         <v>8</v>
       </c>
@@ -18451,17 +18450,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B29&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>2</v>
       </c>
-      <c r="G29" s="141"/>
-      <c r="H29" s="148"/>
-      <c r="I29" s="148"/>
-      <c r="J29" s="148"/>
-      <c r="K29" s="151"/>
-      <c r="L29" s="124"/>
-      <c r="M29" s="118"/>
-      <c r="N29" s="161"/>
+      <c r="G29" s="160"/>
+      <c r="H29" s="151"/>
+      <c r="I29" s="151"/>
+      <c r="J29" s="151"/>
+      <c r="K29" s="154"/>
+      <c r="L29" s="157"/>
+      <c r="M29" s="121"/>
+      <c r="N29" s="118"/>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A30" s="139"/>
+      <c r="A30" s="142"/>
       <c r="B30" s="76" t="s">
         <v>7</v>
       </c>
@@ -18481,17 +18480,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B30&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>0</v>
       </c>
-      <c r="G30" s="141"/>
-      <c r="H30" s="148"/>
-      <c r="I30" s="148"/>
-      <c r="J30" s="148"/>
-      <c r="K30" s="151"/>
-      <c r="L30" s="124"/>
-      <c r="M30" s="118"/>
-      <c r="N30" s="161"/>
+      <c r="G30" s="160"/>
+      <c r="H30" s="151"/>
+      <c r="I30" s="151"/>
+      <c r="J30" s="151"/>
+      <c r="K30" s="154"/>
+      <c r="L30" s="157"/>
+      <c r="M30" s="121"/>
+      <c r="N30" s="118"/>
     </row>
     <row r="31" spans="1:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="139"/>
+      <c r="A31" s="142"/>
       <c r="B31" s="81" t="s">
         <v>272</v>
       </c>
@@ -18511,17 +18510,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B31&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>1</v>
       </c>
-      <c r="G31" s="141"/>
-      <c r="H31" s="148"/>
-      <c r="I31" s="149"/>
-      <c r="J31" s="149"/>
-      <c r="K31" s="152"/>
-      <c r="L31" s="125"/>
-      <c r="M31" s="119"/>
-      <c r="N31" s="162"/>
+      <c r="G31" s="160"/>
+      <c r="H31" s="151"/>
+      <c r="I31" s="152"/>
+      <c r="J31" s="152"/>
+      <c r="K31" s="155"/>
+      <c r="L31" s="158"/>
+      <c r="M31" s="122"/>
+      <c r="N31" s="119"/>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A32" s="126" t="s">
+      <c r="A32" s="123" t="s">
         <v>216</v>
       </c>
       <c r="B32" s="83" t="s">
@@ -18543,41 +18542,41 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B32&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>5</v>
       </c>
-      <c r="G32" s="129">
+      <c r="G32" s="126">
         <f>SUM(C32:C36)</f>
         <v>12</v>
       </c>
-      <c r="H32" s="132">
+      <c r="H32" s="129">
         <f>SUM(D32:D36)</f>
         <v>4</v>
       </c>
-      <c r="I32" s="132">
+      <c r="I32" s="129">
         <f>SUM(E32:E36)</f>
         <v>5</v>
       </c>
-      <c r="J32" s="132">
+      <c r="J32" s="129">
         <f>SUM(F32:F36)</f>
         <v>7</v>
       </c>
-      <c r="K32" s="135">
+      <c r="K32" s="132">
         <f>Q8/G32</f>
         <v>1.2916666666666667E-2</v>
       </c>
-      <c r="L32" s="120">
+      <c r="L32" s="135">
         <f>H32*K32</f>
         <v>5.1666666666666666E-2</v>
       </c>
-      <c r="M32" s="114">
+      <c r="M32" s="138">
         <f>I32*K32</f>
         <v>6.4583333333333326E-2</v>
       </c>
-      <c r="N32" s="163">
+      <c r="N32" s="114">
         <f>J32*K32</f>
         <v>9.0416666666666673E-2</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A33" s="127"/>
+      <c r="A33" s="124"/>
       <c r="B33" s="85" t="s">
         <v>5</v>
       </c>
@@ -18597,18 +18596,18 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B33&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>1</v>
       </c>
-      <c r="G33" s="130"/>
-      <c r="H33" s="133"/>
-      <c r="I33" s="133"/>
-      <c r="J33" s="133"/>
-      <c r="K33" s="136"/>
-      <c r="L33" s="121"/>
-      <c r="M33" s="115"/>
-      <c r="N33" s="164"/>
+      <c r="G33" s="127"/>
+      <c r="H33" s="130"/>
+      <c r="I33" s="130"/>
+      <c r="J33" s="130"/>
+      <c r="K33" s="133"/>
+      <c r="L33" s="136"/>
+      <c r="M33" s="139"/>
+      <c r="N33" s="115"/>
       <c r="Q33" s="79"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A34" s="127"/>
+      <c r="A34" s="124"/>
       <c r="B34" s="85" t="s">
         <v>4</v>
       </c>
@@ -18628,18 +18627,18 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B34&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>0</v>
       </c>
-      <c r="G34" s="130"/>
-      <c r="H34" s="133"/>
-      <c r="I34" s="133"/>
-      <c r="J34" s="133"/>
-      <c r="K34" s="136"/>
-      <c r="L34" s="121"/>
-      <c r="M34" s="115"/>
-      <c r="N34" s="164"/>
+      <c r="G34" s="127"/>
+      <c r="H34" s="130"/>
+      <c r="I34" s="130"/>
+      <c r="J34" s="130"/>
+      <c r="K34" s="133"/>
+      <c r="L34" s="136"/>
+      <c r="M34" s="139"/>
+      <c r="N34" s="115"/>
       <c r="Q34" s="79"/>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A35" s="127"/>
+      <c r="A35" s="124"/>
       <c r="B35" s="85" t="s">
         <v>3</v>
       </c>
@@ -18659,19 +18658,19 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B35&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>1</v>
       </c>
-      <c r="G35" s="130"/>
-      <c r="H35" s="133"/>
-      <c r="I35" s="133"/>
-      <c r="J35" s="133"/>
-      <c r="K35" s="136"/>
-      <c r="L35" s="121"/>
-      <c r="M35" s="115"/>
-      <c r="N35" s="164"/>
+      <c r="G35" s="127"/>
+      <c r="H35" s="130"/>
+      <c r="I35" s="130"/>
+      <c r="J35" s="130"/>
+      <c r="K35" s="133"/>
+      <c r="L35" s="136"/>
+      <c r="M35" s="139"/>
+      <c r="N35" s="115"/>
       <c r="O35" s="79"/>
       <c r="Q35" s="79"/>
     </row>
     <row r="36" spans="1:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="127"/>
+      <c r="A36" s="124"/>
       <c r="B36" s="85" t="s">
         <v>2</v>
       </c>
@@ -18691,20 +18690,20 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B36&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>0</v>
       </c>
-      <c r="G36" s="130"/>
-      <c r="H36" s="133"/>
-      <c r="I36" s="133"/>
-      <c r="J36" s="133"/>
-      <c r="K36" s="137"/>
-      <c r="L36" s="122"/>
-      <c r="M36" s="116"/>
-      <c r="N36" s="165"/>
+      <c r="G36" s="127"/>
+      <c r="H36" s="130"/>
+      <c r="I36" s="130"/>
+      <c r="J36" s="130"/>
+      <c r="K36" s="134"/>
+      <c r="L36" s="137"/>
+      <c r="M36" s="140"/>
+      <c r="N36" s="116"/>
       <c r="O36" s="79"/>
       <c r="P36" s="79"/>
       <c r="Q36" s="79"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A37" s="138" t="s">
+      <c r="A37" s="141" t="s">
         <v>217</v>
       </c>
       <c r="B37" s="71" t="s">
@@ -18726,35 +18725,35 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B37&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>3</v>
       </c>
-      <c r="G37" s="140">
+      <c r="G37" s="159">
         <f>SUM(C37:C42)</f>
         <v>9</v>
       </c>
-      <c r="H37" s="147">
+      <c r="H37" s="150">
         <f t="shared" ref="H37" si="11">SUM(D37:D42)</f>
         <v>5</v>
       </c>
-      <c r="I37" s="147">
+      <c r="I37" s="150">
         <f t="shared" ref="I37" si="12">SUM(E37:E42)</f>
         <v>5</v>
       </c>
-      <c r="J37" s="147">
+      <c r="J37" s="150">
         <f t="shared" ref="J37" si="13">SUM(F37:F42)</f>
         <v>5</v>
       </c>
-      <c r="K37" s="150">
+      <c r="K37" s="161">
         <f>Q9/G37</f>
         <v>7.7777777777777784E-3</v>
       </c>
-      <c r="L37" s="123">
+      <c r="L37" s="156">
         <f>H37*K37</f>
         <v>3.888888888888889E-2</v>
       </c>
-      <c r="M37" s="117">
+      <c r="M37" s="120">
         <f>I37*K37</f>
         <v>3.888888888888889E-2</v>
       </c>
-      <c r="N37" s="160">
+      <c r="N37" s="117">
         <f>J37*K37</f>
         <v>3.888888888888889E-2</v>
       </c>
@@ -18762,7 +18761,7 @@
       <c r="Q37" s="79"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A38" s="139"/>
+      <c r="A38" s="142"/>
       <c r="B38" s="76" t="s">
         <v>578</v>
       </c>
@@ -18782,17 +18781,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B38&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>0</v>
       </c>
-      <c r="G38" s="141"/>
-      <c r="H38" s="148"/>
-      <c r="I38" s="148"/>
-      <c r="J38" s="148"/>
-      <c r="K38" s="151"/>
-      <c r="L38" s="124"/>
-      <c r="M38" s="118"/>
-      <c r="N38" s="161"/>
+      <c r="G38" s="160"/>
+      <c r="H38" s="151"/>
+      <c r="I38" s="151"/>
+      <c r="J38" s="151"/>
+      <c r="K38" s="154"/>
+      <c r="L38" s="157"/>
+      <c r="M38" s="121"/>
+      <c r="N38" s="118"/>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A39" s="139"/>
+      <c r="A39" s="142"/>
       <c r="B39" s="76" t="s">
         <v>579</v>
       </c>
@@ -18812,17 +18811,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B39&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>1</v>
       </c>
-      <c r="G39" s="141"/>
-      <c r="H39" s="148"/>
-      <c r="I39" s="148"/>
-      <c r="J39" s="148"/>
-      <c r="K39" s="151"/>
-      <c r="L39" s="124"/>
-      <c r="M39" s="118"/>
-      <c r="N39" s="161"/>
+      <c r="G39" s="160"/>
+      <c r="H39" s="151"/>
+      <c r="I39" s="151"/>
+      <c r="J39" s="151"/>
+      <c r="K39" s="154"/>
+      <c r="L39" s="157"/>
+      <c r="M39" s="121"/>
+      <c r="N39" s="118"/>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A40" s="139"/>
+      <c r="A40" s="142"/>
       <c r="B40" s="76" t="s">
         <v>580</v>
       </c>
@@ -18842,17 +18841,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B40&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>0</v>
       </c>
-      <c r="G40" s="141"/>
-      <c r="H40" s="148"/>
-      <c r="I40" s="148"/>
-      <c r="J40" s="148"/>
-      <c r="K40" s="151"/>
-      <c r="L40" s="124"/>
-      <c r="M40" s="118"/>
-      <c r="N40" s="161"/>
+      <c r="G40" s="160"/>
+      <c r="H40" s="151"/>
+      <c r="I40" s="151"/>
+      <c r="J40" s="151"/>
+      <c r="K40" s="154"/>
+      <c r="L40" s="157"/>
+      <c r="M40" s="121"/>
+      <c r="N40" s="118"/>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A41" s="139"/>
+      <c r="A41" s="142"/>
       <c r="B41" s="76" t="s">
         <v>581</v>
       </c>
@@ -18872,17 +18871,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B41&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>1</v>
       </c>
-      <c r="G41" s="141"/>
-      <c r="H41" s="148"/>
-      <c r="I41" s="148"/>
-      <c r="J41" s="148"/>
-      <c r="K41" s="151"/>
-      <c r="L41" s="124"/>
-      <c r="M41" s="118"/>
-      <c r="N41" s="161"/>
+      <c r="G41" s="160"/>
+      <c r="H41" s="151"/>
+      <c r="I41" s="151"/>
+      <c r="J41" s="151"/>
+      <c r="K41" s="154"/>
+      <c r="L41" s="157"/>
+      <c r="M41" s="121"/>
+      <c r="N41" s="118"/>
     </row>
     <row r="42" spans="1:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="145"/>
+      <c r="A42" s="143"/>
       <c r="B42" s="81" t="s">
         <v>187</v>
       </c>
@@ -18902,17 +18901,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B42&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>0</v>
       </c>
-      <c r="G42" s="146"/>
-      <c r="H42" s="149"/>
-      <c r="I42" s="149"/>
-      <c r="J42" s="149"/>
-      <c r="K42" s="152"/>
-      <c r="L42" s="125"/>
-      <c r="M42" s="119"/>
-      <c r="N42" s="162"/>
+      <c r="G42" s="162"/>
+      <c r="H42" s="152"/>
+      <c r="I42" s="152"/>
+      <c r="J42" s="152"/>
+      <c r="K42" s="155"/>
+      <c r="L42" s="158"/>
+      <c r="M42" s="122"/>
+      <c r="N42" s="119"/>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A43" s="126" t="s">
+      <c r="A43" s="123" t="s">
         <v>218</v>
       </c>
       <c r="B43" s="83" t="s">
@@ -18934,41 +18933,41 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B43&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>2</v>
       </c>
-      <c r="G43" s="129">
+      <c r="G43" s="126">
         <f>SUM(C43:C47)</f>
         <v>14</v>
       </c>
-      <c r="H43" s="132">
+      <c r="H43" s="129">
         <f t="shared" ref="H43" si="14">SUM(D43:D47)</f>
         <v>10</v>
       </c>
-      <c r="I43" s="132">
+      <c r="I43" s="129">
         <f t="shared" ref="I43" si="15">SUM(E43:E47)</f>
         <v>11</v>
       </c>
-      <c r="J43" s="132">
+      <c r="J43" s="129">
         <f t="shared" ref="J43" si="16">SUM(F43:F47)</f>
         <v>9</v>
       </c>
-      <c r="K43" s="135">
+      <c r="K43" s="132">
         <f>Q10/G43</f>
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="L43" s="120">
+      <c r="L43" s="135">
         <f>H43*K43</f>
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="M43" s="114">
+      <c r="M43" s="138">
         <f>I43*K43</f>
         <v>8.249999999999999E-2</v>
       </c>
-      <c r="N43" s="163">
+      <c r="N43" s="114">
         <f>J43*K43</f>
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A44" s="127"/>
+      <c r="A44" s="124"/>
       <c r="B44" s="85" t="s">
         <v>538</v>
       </c>
@@ -18988,17 +18987,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B44&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>3</v>
       </c>
-      <c r="G44" s="130"/>
-      <c r="H44" s="133"/>
-      <c r="I44" s="133"/>
-      <c r="J44" s="133"/>
-      <c r="K44" s="136"/>
-      <c r="L44" s="121"/>
-      <c r="M44" s="115"/>
-      <c r="N44" s="164"/>
+      <c r="G44" s="127"/>
+      <c r="H44" s="130"/>
+      <c r="I44" s="130"/>
+      <c r="J44" s="130"/>
+      <c r="K44" s="133"/>
+      <c r="L44" s="136"/>
+      <c r="M44" s="139"/>
+      <c r="N44" s="115"/>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A45" s="127"/>
+      <c r="A45" s="124"/>
       <c r="B45" s="85" t="s">
         <v>540</v>
       </c>
@@ -19018,17 +19017,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B45&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>0</v>
       </c>
-      <c r="G45" s="130"/>
-      <c r="H45" s="133"/>
-      <c r="I45" s="133"/>
-      <c r="J45" s="133"/>
-      <c r="K45" s="136"/>
-      <c r="L45" s="121"/>
-      <c r="M45" s="115"/>
-      <c r="N45" s="164"/>
+      <c r="G45" s="127"/>
+      <c r="H45" s="130"/>
+      <c r="I45" s="130"/>
+      <c r="J45" s="130"/>
+      <c r="K45" s="133"/>
+      <c r="L45" s="136"/>
+      <c r="M45" s="139"/>
+      <c r="N45" s="115"/>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A46" s="127"/>
+      <c r="A46" s="124"/>
       <c r="B46" s="85" t="s">
         <v>541</v>
       </c>
@@ -19048,17 +19047,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B46&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>2</v>
       </c>
-      <c r="G46" s="130"/>
-      <c r="H46" s="133"/>
-      <c r="I46" s="133"/>
-      <c r="J46" s="133"/>
-      <c r="K46" s="136"/>
-      <c r="L46" s="121"/>
-      <c r="M46" s="115"/>
-      <c r="N46" s="164"/>
+      <c r="G46" s="127"/>
+      <c r="H46" s="130"/>
+      <c r="I46" s="130"/>
+      <c r="J46" s="130"/>
+      <c r="K46" s="133"/>
+      <c r="L46" s="136"/>
+      <c r="M46" s="139"/>
+      <c r="N46" s="115"/>
     </row>
     <row r="47" spans="1:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="128"/>
+      <c r="A47" s="125"/>
       <c r="B47" s="98" t="s">
         <v>543</v>
       </c>
@@ -19078,17 +19077,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B47&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>2</v>
       </c>
-      <c r="G47" s="131"/>
-      <c r="H47" s="134"/>
-      <c r="I47" s="134"/>
-      <c r="J47" s="134"/>
-      <c r="K47" s="137"/>
-      <c r="L47" s="122"/>
-      <c r="M47" s="116"/>
-      <c r="N47" s="165"/>
+      <c r="G47" s="128"/>
+      <c r="H47" s="131"/>
+      <c r="I47" s="131"/>
+      <c r="J47" s="131"/>
+      <c r="K47" s="134"/>
+      <c r="L47" s="137"/>
+      <c r="M47" s="140"/>
+      <c r="N47" s="116"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A48" s="138" t="s">
+      <c r="A48" s="141" t="s">
         <v>219</v>
       </c>
       <c r="B48" s="71" t="s">
@@ -19110,42 +19109,42 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B48&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>2</v>
       </c>
-      <c r="G48" s="140">
+      <c r="G48" s="159">
         <f>SUM(C48:C52)</f>
         <v>6</v>
       </c>
-      <c r="H48" s="142">
+      <c r="H48" s="163">
         <f t="shared" ref="H48" si="17">SUM(D48:D52)</f>
         <v>3</v>
       </c>
-      <c r="I48" s="142">
+      <c r="I48" s="163">
         <f t="shared" ref="I48" si="18">SUM(E48:E52)</f>
         <v>3</v>
       </c>
-      <c r="J48" s="142">
+      <c r="J48" s="163">
         <f t="shared" ref="J48" si="19">SUM(F48:F52)</f>
         <v>10</v>
       </c>
-      <c r="K48" s="144">
+      <c r="K48" s="165">
         <f>Q11/G48</f>
         <v>6.6666666666666671E-3</v>
       </c>
-      <c r="L48" s="123">
+      <c r="L48" s="156">
         <f>H48*K48</f>
         <v>0.02</v>
       </c>
-      <c r="M48" s="117">
+      <c r="M48" s="120">
         <f>I48*K48</f>
         <v>0.02</v>
       </c>
-      <c r="N48" s="160">
+      <c r="N48" s="117">
         <f>J48*K48</f>
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="O48" s="101"/>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A49" s="139"/>
+      <c r="A49" s="142"/>
       <c r="B49" s="102" t="s">
         <v>66</v>
       </c>
@@ -19165,18 +19164,18 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B49&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>3</v>
       </c>
-      <c r="G49" s="141"/>
-      <c r="H49" s="143"/>
-      <c r="I49" s="143"/>
-      <c r="J49" s="143"/>
-      <c r="K49" s="144"/>
-      <c r="L49" s="124"/>
-      <c r="M49" s="118"/>
-      <c r="N49" s="161"/>
+      <c r="G49" s="160"/>
+      <c r="H49" s="164"/>
+      <c r="I49" s="164"/>
+      <c r="J49" s="164"/>
+      <c r="K49" s="165"/>
+      <c r="L49" s="157"/>
+      <c r="M49" s="121"/>
+      <c r="N49" s="118"/>
       <c r="P49" s="101"/>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A50" s="139"/>
+      <c r="A50" s="142"/>
       <c r="B50" s="76" t="s">
         <v>67</v>
       </c>
@@ -19196,18 +19195,18 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B50&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>3</v>
       </c>
-      <c r="G50" s="141"/>
-      <c r="H50" s="143"/>
-      <c r="I50" s="143"/>
-      <c r="J50" s="143"/>
-      <c r="K50" s="144"/>
-      <c r="L50" s="124"/>
-      <c r="M50" s="118"/>
-      <c r="N50" s="161"/>
+      <c r="G50" s="160"/>
+      <c r="H50" s="164"/>
+      <c r="I50" s="164"/>
+      <c r="J50" s="164"/>
+      <c r="K50" s="165"/>
+      <c r="L50" s="157"/>
+      <c r="M50" s="121"/>
+      <c r="N50" s="118"/>
       <c r="O50" s="101"/>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A51" s="139"/>
+      <c r="A51" s="142"/>
       <c r="B51" s="76" t="s">
         <v>68</v>
       </c>
@@ -19227,18 +19226,18 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B51&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>1</v>
       </c>
-      <c r="G51" s="141"/>
-      <c r="H51" s="143"/>
-      <c r="I51" s="143"/>
-      <c r="J51" s="143"/>
-      <c r="K51" s="144"/>
-      <c r="L51" s="124"/>
-      <c r="M51" s="118"/>
-      <c r="N51" s="161"/>
+      <c r="G51" s="160"/>
+      <c r="H51" s="164"/>
+      <c r="I51" s="164"/>
+      <c r="J51" s="164"/>
+      <c r="K51" s="165"/>
+      <c r="L51" s="157"/>
+      <c r="M51" s="121"/>
+      <c r="N51" s="118"/>
       <c r="P51" s="101"/>
     </row>
     <row r="52" spans="1:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="139"/>
+      <c r="A52" s="142"/>
       <c r="B52" s="102" t="s">
         <v>69</v>
       </c>
@@ -19258,17 +19257,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B52&amp;"*",Evaluation!$A$2:$A$142,"&lt;&gt;*X*")</f>
         <v>1</v>
       </c>
-      <c r="G52" s="141"/>
-      <c r="H52" s="143"/>
-      <c r="I52" s="143"/>
-      <c r="J52" s="143"/>
-      <c r="K52" s="144"/>
-      <c r="L52" s="125"/>
-      <c r="M52" s="119"/>
-      <c r="N52" s="162"/>
+      <c r="G52" s="160"/>
+      <c r="H52" s="164"/>
+      <c r="I52" s="164"/>
+      <c r="J52" s="164"/>
+      <c r="K52" s="165"/>
+      <c r="L52" s="158"/>
+      <c r="M52" s="122"/>
+      <c r="N52" s="119"/>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A53" s="126" t="s">
+      <c r="A53" s="123" t="s">
         <v>220</v>
       </c>
       <c r="B53" s="83" t="s">
@@ -19290,41 +19289,41 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B53&amp;"*")</f>
         <v>1</v>
       </c>
-      <c r="G53" s="129">
+      <c r="G53" s="126">
         <f>SUM(C53:C69)</f>
         <v>10</v>
       </c>
-      <c r="H53" s="132">
+      <c r="H53" s="129">
         <f>SUM(D53:D69)</f>
         <v>1</v>
       </c>
-      <c r="I53" s="132">
+      <c r="I53" s="129">
         <f>SUM(E53:E69)</f>
         <v>1</v>
       </c>
-      <c r="J53" s="132">
+      <c r="J53" s="129">
         <f>SUM(F53:F69)</f>
         <v>14</v>
       </c>
-      <c r="K53" s="135">
+      <c r="K53" s="132">
         <f>0.01</f>
         <v>0.01</v>
       </c>
-      <c r="L53" s="120">
+      <c r="L53" s="135">
         <f>H53*K53</f>
         <v>0.01</v>
       </c>
-      <c r="M53" s="114">
+      <c r="M53" s="138">
         <f>I53*K53</f>
         <v>0.01</v>
       </c>
-      <c r="N53" s="163">
+      <c r="N53" s="114">
         <f>J53*K53</f>
         <v>0.14000000000000001</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A54" s="127"/>
+      <c r="A54" s="124"/>
       <c r="B54" s="85" t="s">
         <v>49</v>
       </c>
@@ -19344,17 +19343,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B54&amp;"*")</f>
         <v>1</v>
       </c>
-      <c r="G54" s="130"/>
-      <c r="H54" s="133"/>
-      <c r="I54" s="133"/>
-      <c r="J54" s="133"/>
-      <c r="K54" s="136"/>
-      <c r="L54" s="121"/>
-      <c r="M54" s="115"/>
-      <c r="N54" s="164"/>
+      <c r="G54" s="127"/>
+      <c r="H54" s="130"/>
+      <c r="I54" s="130"/>
+      <c r="J54" s="130"/>
+      <c r="K54" s="133"/>
+      <c r="L54" s="136"/>
+      <c r="M54" s="139"/>
+      <c r="N54" s="115"/>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A55" s="127"/>
+      <c r="A55" s="124"/>
       <c r="B55" s="85" t="s">
         <v>249</v>
       </c>
@@ -19374,17 +19373,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B55&amp;"*")</f>
         <v>1</v>
       </c>
-      <c r="G55" s="130"/>
-      <c r="H55" s="133"/>
-      <c r="I55" s="133"/>
-      <c r="J55" s="133"/>
-      <c r="K55" s="136"/>
-      <c r="L55" s="121"/>
-      <c r="M55" s="115"/>
-      <c r="N55" s="164"/>
+      <c r="G55" s="127"/>
+      <c r="H55" s="130"/>
+      <c r="I55" s="130"/>
+      <c r="J55" s="130"/>
+      <c r="K55" s="133"/>
+      <c r="L55" s="136"/>
+      <c r="M55" s="139"/>
+      <c r="N55" s="115"/>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A56" s="127"/>
+      <c r="A56" s="124"/>
       <c r="B56" s="85" t="s">
         <v>51</v>
       </c>
@@ -19404,17 +19403,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B56&amp;"*")</f>
         <v>0</v>
       </c>
-      <c r="G56" s="130"/>
-      <c r="H56" s="133"/>
-      <c r="I56" s="133"/>
-      <c r="J56" s="133"/>
-      <c r="K56" s="136"/>
-      <c r="L56" s="121"/>
-      <c r="M56" s="115"/>
-      <c r="N56" s="164"/>
+      <c r="G56" s="127"/>
+      <c r="H56" s="130"/>
+      <c r="I56" s="130"/>
+      <c r="J56" s="130"/>
+      <c r="K56" s="133"/>
+      <c r="L56" s="136"/>
+      <c r="M56" s="139"/>
+      <c r="N56" s="115"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A57" s="127"/>
+      <c r="A57" s="124"/>
       <c r="B57" s="85" t="s">
         <v>260</v>
       </c>
@@ -19434,17 +19433,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B57&amp;"*")</f>
         <v>1</v>
       </c>
-      <c r="G57" s="130"/>
-      <c r="H57" s="133"/>
-      <c r="I57" s="133"/>
-      <c r="J57" s="133"/>
-      <c r="K57" s="136"/>
-      <c r="L57" s="121"/>
-      <c r="M57" s="115"/>
-      <c r="N57" s="164"/>
+      <c r="G57" s="127"/>
+      <c r="H57" s="130"/>
+      <c r="I57" s="130"/>
+      <c r="J57" s="130"/>
+      <c r="K57" s="133"/>
+      <c r="L57" s="136"/>
+      <c r="M57" s="139"/>
+      <c r="N57" s="115"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A58" s="127"/>
+      <c r="A58" s="124"/>
       <c r="B58" s="85" t="s">
         <v>582</v>
       </c>
@@ -19464,17 +19463,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B58&amp;"*")</f>
         <v>1</v>
       </c>
-      <c r="G58" s="130"/>
-      <c r="H58" s="133"/>
-      <c r="I58" s="133"/>
-      <c r="J58" s="133"/>
-      <c r="K58" s="136"/>
-      <c r="L58" s="121"/>
-      <c r="M58" s="115"/>
-      <c r="N58" s="164"/>
+      <c r="G58" s="127"/>
+      <c r="H58" s="130"/>
+      <c r="I58" s="130"/>
+      <c r="J58" s="130"/>
+      <c r="K58" s="133"/>
+      <c r="L58" s="136"/>
+      <c r="M58" s="139"/>
+      <c r="N58" s="115"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A59" s="127"/>
+      <c r="A59" s="124"/>
       <c r="B59" s="85" t="s">
         <v>55</v>
       </c>
@@ -19494,17 +19493,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B59&amp;"*")</f>
         <v>0</v>
       </c>
-      <c r="G59" s="130"/>
-      <c r="H59" s="133"/>
-      <c r="I59" s="133"/>
-      <c r="J59" s="133"/>
-      <c r="K59" s="136"/>
-      <c r="L59" s="121"/>
-      <c r="M59" s="115"/>
-      <c r="N59" s="164"/>
+      <c r="G59" s="127"/>
+      <c r="H59" s="130"/>
+      <c r="I59" s="130"/>
+      <c r="J59" s="130"/>
+      <c r="K59" s="133"/>
+      <c r="L59" s="136"/>
+      <c r="M59" s="139"/>
+      <c r="N59" s="115"/>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A60" s="127"/>
+      <c r="A60" s="124"/>
       <c r="B60" s="85" t="s">
         <v>235</v>
       </c>
@@ -19524,17 +19523,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B60&amp;"*")</f>
         <v>4</v>
       </c>
-      <c r="G60" s="130"/>
-      <c r="H60" s="133"/>
-      <c r="I60" s="133"/>
-      <c r="J60" s="133"/>
-      <c r="K60" s="136"/>
-      <c r="L60" s="121"/>
-      <c r="M60" s="115"/>
-      <c r="N60" s="164"/>
+      <c r="G60" s="127"/>
+      <c r="H60" s="130"/>
+      <c r="I60" s="130"/>
+      <c r="J60" s="130"/>
+      <c r="K60" s="133"/>
+      <c r="L60" s="136"/>
+      <c r="M60" s="139"/>
+      <c r="N60" s="115"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A61" s="127"/>
+      <c r="A61" s="124"/>
       <c r="B61" s="85" t="s">
         <v>59</v>
       </c>
@@ -19554,17 +19553,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B61&amp;"*")</f>
         <v>0</v>
       </c>
-      <c r="G61" s="130"/>
-      <c r="H61" s="133"/>
-      <c r="I61" s="133"/>
-      <c r="J61" s="133"/>
-      <c r="K61" s="136"/>
-      <c r="L61" s="121"/>
-      <c r="M61" s="115"/>
-      <c r="N61" s="164"/>
+      <c r="G61" s="127"/>
+      <c r="H61" s="130"/>
+      <c r="I61" s="130"/>
+      <c r="J61" s="130"/>
+      <c r="K61" s="133"/>
+      <c r="L61" s="136"/>
+      <c r="M61" s="139"/>
+      <c r="N61" s="115"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A62" s="127"/>
+      <c r="A62" s="124"/>
       <c r="B62" s="85" t="s">
         <v>274</v>
       </c>
@@ -19584,17 +19583,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B62&amp;"*")</f>
         <v>1</v>
       </c>
-      <c r="G62" s="130"/>
-      <c r="H62" s="133"/>
-      <c r="I62" s="133"/>
-      <c r="J62" s="133"/>
-      <c r="K62" s="136"/>
-      <c r="L62" s="121"/>
-      <c r="M62" s="115"/>
-      <c r="N62" s="164"/>
+      <c r="G62" s="127"/>
+      <c r="H62" s="130"/>
+      <c r="I62" s="130"/>
+      <c r="J62" s="130"/>
+      <c r="K62" s="133"/>
+      <c r="L62" s="136"/>
+      <c r="M62" s="139"/>
+      <c r="N62" s="115"/>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A63" s="127"/>
+      <c r="A63" s="124"/>
       <c r="B63" s="85" t="s">
         <v>63</v>
       </c>
@@ -19614,17 +19613,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B63&amp;"*")</f>
         <v>2</v>
       </c>
-      <c r="G63" s="130"/>
-      <c r="H63" s="133"/>
-      <c r="I63" s="133"/>
-      <c r="J63" s="133"/>
-      <c r="K63" s="136"/>
-      <c r="L63" s="121"/>
-      <c r="M63" s="115"/>
-      <c r="N63" s="164"/>
+      <c r="G63" s="127"/>
+      <c r="H63" s="130"/>
+      <c r="I63" s="130"/>
+      <c r="J63" s="130"/>
+      <c r="K63" s="133"/>
+      <c r="L63" s="136"/>
+      <c r="M63" s="139"/>
+      <c r="N63" s="115"/>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A64" s="127"/>
+      <c r="A64" s="124"/>
       <c r="B64" s="85" t="s">
         <v>64</v>
       </c>
@@ -19644,17 +19643,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B64&amp;"*")</f>
         <v>0</v>
       </c>
-      <c r="G64" s="130"/>
-      <c r="H64" s="133"/>
-      <c r="I64" s="133"/>
-      <c r="J64" s="133"/>
-      <c r="K64" s="136"/>
-      <c r="L64" s="121"/>
-      <c r="M64" s="115"/>
-      <c r="N64" s="164"/>
+      <c r="G64" s="127"/>
+      <c r="H64" s="130"/>
+      <c r="I64" s="130"/>
+      <c r="J64" s="130"/>
+      <c r="K64" s="133"/>
+      <c r="L64" s="136"/>
+      <c r="M64" s="139"/>
+      <c r="N64" s="115"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A65" s="127"/>
+      <c r="A65" s="124"/>
       <c r="B65" s="85" t="s">
         <v>583</v>
       </c>
@@ -19674,17 +19673,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B65&amp;"*")</f>
         <v>0</v>
       </c>
-      <c r="G65" s="130"/>
-      <c r="H65" s="133"/>
-      <c r="I65" s="133"/>
-      <c r="J65" s="133"/>
-      <c r="K65" s="136"/>
-      <c r="L65" s="121"/>
-      <c r="M65" s="115"/>
-      <c r="N65" s="164"/>
+      <c r="G65" s="127"/>
+      <c r="H65" s="130"/>
+      <c r="I65" s="130"/>
+      <c r="J65" s="130"/>
+      <c r="K65" s="133"/>
+      <c r="L65" s="136"/>
+      <c r="M65" s="139"/>
+      <c r="N65" s="115"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A66" s="127"/>
+      <c r="A66" s="124"/>
       <c r="B66" s="85" t="s">
         <v>584</v>
       </c>
@@ -19704,17 +19703,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B66&amp;"*")</f>
         <v>0</v>
       </c>
-      <c r="G66" s="130"/>
-      <c r="H66" s="133"/>
-      <c r="I66" s="133"/>
-      <c r="J66" s="133"/>
-      <c r="K66" s="136"/>
-      <c r="L66" s="121"/>
-      <c r="M66" s="115"/>
-      <c r="N66" s="164"/>
+      <c r="G66" s="127"/>
+      <c r="H66" s="130"/>
+      <c r="I66" s="130"/>
+      <c r="J66" s="130"/>
+      <c r="K66" s="133"/>
+      <c r="L66" s="136"/>
+      <c r="M66" s="139"/>
+      <c r="N66" s="115"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A67" s="127"/>
+      <c r="A67" s="124"/>
       <c r="B67" s="85" t="s">
         <v>585</v>
       </c>
@@ -19734,17 +19733,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B67&amp;"*")</f>
         <v>1</v>
       </c>
-      <c r="G67" s="130"/>
-      <c r="H67" s="133"/>
-      <c r="I67" s="133"/>
-      <c r="J67" s="133"/>
-      <c r="K67" s="136"/>
-      <c r="L67" s="121"/>
-      <c r="M67" s="115"/>
-      <c r="N67" s="164"/>
+      <c r="G67" s="127"/>
+      <c r="H67" s="130"/>
+      <c r="I67" s="130"/>
+      <c r="J67" s="130"/>
+      <c r="K67" s="133"/>
+      <c r="L67" s="136"/>
+      <c r="M67" s="139"/>
+      <c r="N67" s="115"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A68" s="127"/>
+      <c r="A68" s="124"/>
       <c r="B68" s="85" t="s">
         <v>539</v>
       </c>
@@ -19764,17 +19763,17 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B68&amp;"*")</f>
         <v>0</v>
       </c>
-      <c r="G68" s="130"/>
-      <c r="H68" s="133"/>
-      <c r="I68" s="133"/>
-      <c r="J68" s="133"/>
-      <c r="K68" s="136"/>
-      <c r="L68" s="121"/>
-      <c r="M68" s="115"/>
-      <c r="N68" s="164"/>
+      <c r="G68" s="127"/>
+      <c r="H68" s="130"/>
+      <c r="I68" s="130"/>
+      <c r="J68" s="130"/>
+      <c r="K68" s="133"/>
+      <c r="L68" s="136"/>
+      <c r="M68" s="139"/>
+      <c r="N68" s="115"/>
     </row>
     <row r="69" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="128"/>
+      <c r="A69" s="125"/>
       <c r="B69" s="98" t="s">
         <v>542</v>
       </c>
@@ -19794,27 +19793,81 @@
         <f>SUMIFS(Evaluation!$I$2:$I$142,Evaluation!$A$2:$A$142,$B69&amp;"*")</f>
         <v>1</v>
       </c>
-      <c r="G69" s="131"/>
-      <c r="H69" s="134"/>
-      <c r="I69" s="134"/>
-      <c r="J69" s="134"/>
-      <c r="K69" s="137"/>
-      <c r="L69" s="122"/>
-      <c r="M69" s="116"/>
-      <c r="N69" s="165"/>
+      <c r="G69" s="128"/>
+      <c r="H69" s="131"/>
+      <c r="I69" s="131"/>
+      <c r="J69" s="131"/>
+      <c r="K69" s="134"/>
+      <c r="L69" s="137"/>
+      <c r="M69" s="140"/>
+      <c r="N69" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="90">
-    <mergeCell ref="N32:N36"/>
-    <mergeCell ref="N37:N42"/>
-    <mergeCell ref="N43:N47"/>
-    <mergeCell ref="N48:N52"/>
-    <mergeCell ref="N53:N69"/>
-    <mergeCell ref="N2:N6"/>
-    <mergeCell ref="N7:N16"/>
-    <mergeCell ref="N17:N24"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="N27:N31"/>
+    <mergeCell ref="M53:M69"/>
+    <mergeCell ref="M48:M52"/>
+    <mergeCell ref="L53:L69"/>
+    <mergeCell ref="L48:L52"/>
+    <mergeCell ref="A53:A69"/>
+    <mergeCell ref="G53:G69"/>
+    <mergeCell ref="H53:H69"/>
+    <mergeCell ref="J53:J69"/>
+    <mergeCell ref="K53:K69"/>
+    <mergeCell ref="I53:I69"/>
+    <mergeCell ref="A48:A52"/>
+    <mergeCell ref="G48:G52"/>
+    <mergeCell ref="H48:H52"/>
+    <mergeCell ref="J48:J52"/>
+    <mergeCell ref="K48:K52"/>
+    <mergeCell ref="I48:I52"/>
+    <mergeCell ref="M37:M42"/>
+    <mergeCell ref="A43:A47"/>
+    <mergeCell ref="G43:G47"/>
+    <mergeCell ref="H43:H47"/>
+    <mergeCell ref="J43:J47"/>
+    <mergeCell ref="K43:K47"/>
+    <mergeCell ref="L43:L47"/>
+    <mergeCell ref="M43:M47"/>
+    <mergeCell ref="A37:A42"/>
+    <mergeCell ref="G37:G42"/>
+    <mergeCell ref="H37:H42"/>
+    <mergeCell ref="J37:J42"/>
+    <mergeCell ref="K37:K42"/>
+    <mergeCell ref="L37:L42"/>
+    <mergeCell ref="I37:I42"/>
+    <mergeCell ref="I43:I47"/>
+    <mergeCell ref="M27:M31"/>
+    <mergeCell ref="A32:A36"/>
+    <mergeCell ref="G32:G36"/>
+    <mergeCell ref="H32:H36"/>
+    <mergeCell ref="J32:J36"/>
+    <mergeCell ref="K32:K36"/>
+    <mergeCell ref="L32:L36"/>
+    <mergeCell ref="M32:M36"/>
+    <mergeCell ref="A27:A31"/>
+    <mergeCell ref="G27:G31"/>
+    <mergeCell ref="H27:H31"/>
+    <mergeCell ref="J27:J31"/>
+    <mergeCell ref="K27:K31"/>
+    <mergeCell ref="L27:L31"/>
+    <mergeCell ref="I27:I31"/>
+    <mergeCell ref="I32:I36"/>
+    <mergeCell ref="M17:M24"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="K25:K26"/>
+    <mergeCell ref="L25:L26"/>
+    <mergeCell ref="M25:M26"/>
+    <mergeCell ref="A17:A24"/>
+    <mergeCell ref="G17:G24"/>
+    <mergeCell ref="H17:H24"/>
+    <mergeCell ref="J17:J24"/>
+    <mergeCell ref="K17:K24"/>
+    <mergeCell ref="L17:L24"/>
+    <mergeCell ref="I17:I24"/>
+    <mergeCell ref="I25:I26"/>
     <mergeCell ref="M2:M6"/>
     <mergeCell ref="A7:A16"/>
     <mergeCell ref="G7:G16"/>
@@ -19831,70 +19884,16 @@
     <mergeCell ref="L2:L6"/>
     <mergeCell ref="I2:I6"/>
     <mergeCell ref="I7:I16"/>
-    <mergeCell ref="M17:M24"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="K25:K26"/>
-    <mergeCell ref="L25:L26"/>
-    <mergeCell ref="M25:M26"/>
-    <mergeCell ref="A17:A24"/>
-    <mergeCell ref="G17:G24"/>
-    <mergeCell ref="H17:H24"/>
-    <mergeCell ref="J17:J24"/>
-    <mergeCell ref="K17:K24"/>
-    <mergeCell ref="L17:L24"/>
-    <mergeCell ref="I17:I24"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="M27:M31"/>
-    <mergeCell ref="A32:A36"/>
-    <mergeCell ref="G32:G36"/>
-    <mergeCell ref="H32:H36"/>
-    <mergeCell ref="J32:J36"/>
-    <mergeCell ref="K32:K36"/>
-    <mergeCell ref="L32:L36"/>
-    <mergeCell ref="M32:M36"/>
-    <mergeCell ref="A27:A31"/>
-    <mergeCell ref="G27:G31"/>
-    <mergeCell ref="H27:H31"/>
-    <mergeCell ref="J27:J31"/>
-    <mergeCell ref="K27:K31"/>
-    <mergeCell ref="L27:L31"/>
-    <mergeCell ref="I27:I31"/>
-    <mergeCell ref="I32:I36"/>
-    <mergeCell ref="M37:M42"/>
-    <mergeCell ref="A43:A47"/>
-    <mergeCell ref="G43:G47"/>
-    <mergeCell ref="H43:H47"/>
-    <mergeCell ref="J43:J47"/>
-    <mergeCell ref="K43:K47"/>
-    <mergeCell ref="L43:L47"/>
-    <mergeCell ref="M43:M47"/>
-    <mergeCell ref="A37:A42"/>
-    <mergeCell ref="G37:G42"/>
-    <mergeCell ref="H37:H42"/>
-    <mergeCell ref="J37:J42"/>
-    <mergeCell ref="K37:K42"/>
-    <mergeCell ref="L37:L42"/>
-    <mergeCell ref="I37:I42"/>
-    <mergeCell ref="I43:I47"/>
-    <mergeCell ref="M53:M69"/>
-    <mergeCell ref="M48:M52"/>
-    <mergeCell ref="L53:L69"/>
-    <mergeCell ref="L48:L52"/>
-    <mergeCell ref="A53:A69"/>
-    <mergeCell ref="G53:G69"/>
-    <mergeCell ref="H53:H69"/>
-    <mergeCell ref="J53:J69"/>
-    <mergeCell ref="K53:K69"/>
-    <mergeCell ref="I53:I69"/>
-    <mergeCell ref="A48:A52"/>
-    <mergeCell ref="G48:G52"/>
-    <mergeCell ref="H48:H52"/>
-    <mergeCell ref="J48:J52"/>
-    <mergeCell ref="K48:K52"/>
-    <mergeCell ref="I48:I52"/>
+    <mergeCell ref="N2:N6"/>
+    <mergeCell ref="N7:N16"/>
+    <mergeCell ref="N17:N24"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="N27:N31"/>
+    <mergeCell ref="N32:N36"/>
+    <mergeCell ref="N37:N42"/>
+    <mergeCell ref="N43:N47"/>
+    <mergeCell ref="N48:N52"/>
+    <mergeCell ref="N53:N69"/>
   </mergeCells>
   <conditionalFormatting sqref="R14:T14">
     <cfRule type="colorScale" priority="1">
@@ -19909,7 +19908,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q1" xr:uid="{33FCD1D3-F91C-4367-A37A-E2928C9EEF14}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q1">
       <formula1>$Z$2:$AB$2</formula1>
     </dataValidation>
   </dataValidations>
@@ -19920,7 +19919,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -20573,12 +20572,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="Q4:V15">
-    <cfRule type="expression" dxfId="1" priority="16">
+    <cfRule type="expression" dxfId="14" priority="16">
       <formula>AND($G4=0,$D4&lt;&gt; "Prérequis")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q17:V17">
-    <cfRule type="expression" dxfId="0" priority="14">
+    <cfRule type="expression" dxfId="13" priority="14">
       <formula>AND($G17=0,$D17&lt;&gt; "Prérequis")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20602,15 +20601,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003C21C7F79DA7D44C9202BD863DBD3895" ma:contentTypeVersion="15" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="fed637fa7e1d143a204cefcb6187e972">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ec407b85-22e9-43a2-9ee3-8399a223d44b" xmlns:ns3="4e14dbf3-4757-4b87-830c-f81c5995cb21" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="89ed423d9bbd7ae496afd80ebb04f7a8" ns2:_="" ns3:_="">
     <xsd:import namespace="ec407b85-22e9-43a2-9ee3-8399a223d44b"/>
@@ -20845,6 +20835,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{978BAAE8-B782-4F63-A92B-D383B00FEA5B}">
   <ds:schemaRefs>
@@ -20863,14 +20862,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96477EE0-D69D-494E-A267-59EBF2123547}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86D89662-BC7E-433B-A0D7-3034BA5A324E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20887,4 +20878,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96477EE0-D69D-494E-A267-59EBF2123547}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>